--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F333D1-B31C-4878-BBB9-42096CC3B428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEA380E-1576-4B11-A6DB-5A1C3751D0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22046" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="147">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -747,6 +747,46 @@
   </si>
   <si>
     <t>창을 닫으면 설정이 적용 됩니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Inventory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aromor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>アイテム</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防具（ぼうぐ）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器（ぶき）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1175,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:D54"/>
+  <dimension ref="A2:D62"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -1883,9 +1923,69 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="53" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A52" s="2">
+        <v>9000049</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A53" s="3">
+        <v>9000050</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A54" s="2">
+        <v>9000051</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A55" s="3">
+        <v>9000052</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="57" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="59" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="61" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEA380E-1576-4B11-A6DB-5A1C3751D0A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A4738A-501C-417A-8C7E-623DB89AD384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="165">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -787,6 +787,114 @@
   </si>
   <si>
     <t>武器（ぶき）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空欄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Empty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비어 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>레어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엘리트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>에픽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>レジェンダリ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>レア</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>エリ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ート</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>エピック</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ノ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ーマル</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1979,12 +2087,90 @@
         <v>146</v>
       </c>
     </row>
-    <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="57" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="59" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="61" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="56" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A56" s="2">
+        <v>9000053</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A57" s="3">
+        <v>9000054</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A58" s="2">
+        <v>9000055</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A59" s="3">
+        <v>9000056</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A60" s="2">
+        <v>9000057</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A61" s="3">
+        <v>9000058</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
     <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A4738A-501C-417A-8C7E-623DB89AD384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADFAD89-0F21-4458-9DB7-B690435F9792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="171">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -894,6 +894,54 @@
         <charset val="128"/>
       </rPr>
       <t>ーマル</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Daily</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>デイリ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Weekly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ウィ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ークリー</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1323,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:D62"/>
+  <dimension ref="A2:D78"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
@@ -2171,7 +2219,51 @@
         <v>160</v>
       </c>
     </row>
-    <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="62" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A62" s="2">
+        <v>9000059</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A63" s="3">
+        <v>9000060</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="65" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="66" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="67" spans="4:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="D67" s="4"/>
+    </row>
+    <row r="68" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="69" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="70" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="71" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="72" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="73" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="74" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="75" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="76" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="77" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="78" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADFAD89-0F21-4458-9DB7-B690435F9792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9D8B4-81B1-40F3-93D8-5526F742D32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="190">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -943,6 +943,118 @@
       </rPr>
       <t>ークリー</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어 경험치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Player EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>プレイヤ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ー経験値</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고 도달 스테이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Highest Stage Reached</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>最高到達ステ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ージ</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유 캐릭터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정 생성일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메모</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メモ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>アカウント作成日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>所持キャラクタ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ー</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Owned Characters</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Account Creation Date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UID {0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2247,23 +2359,112 @@
         <v>170</v>
       </c>
     </row>
-    <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="65" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="66" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="67" spans="4:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="69" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="70" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="71" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="72" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="73" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="74" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="75" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="76" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="77" spans="4:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
-    <row r="78" spans="4:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="64" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A64" s="2">
+        <v>9000061</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A65" s="3">
+        <v>9000062</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" s="2" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A66" s="2">
+        <v>9000063</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" s="3" customFormat="1" ht="17.649999999999999" x14ac:dyDescent="0.6">
+      <c r="A67" s="3">
+        <v>9000064</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A68" s="2">
+        <v>9000065</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A69" s="3">
+        <v>9000066</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A70" s="2">
+        <v>9000067</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="73" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="75" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="76" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="77" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="78" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD9D8B4-81B1-40F3-93D8-5526F742D32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17979C0-6C26-44C0-9F1C-D860661F8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-21510" yWindow="2440" windowWidth="21600" windowHeight="11330" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -1054,7 +1054,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>UID {0}</t>
+    <t>UID. {0}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/_900_CommonText.xlsx
+++ b/_900_CommonText.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17979C0-6C26-44C0-9F1C-D860661F8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4F7789-1A03-4106-8C5E-D09490BF9F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21510" yWindow="2440" windowWidth="21600" windowHeight="11330" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
